--- a/data/trans_dic/P15D$ingresado-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15D$ingresado-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,7</t>
+          <t>0,0; 51,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 27,93</t>
+          <t>4,36; 25,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,5</t>
+          <t>0,0; 21,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,17</t>
+          <t>0,0; 23,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 40,7</t>
+          <t>7,23; 38,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 15,68</t>
+          <t>1,63; 15,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,46</t>
+          <t>0,0; 36,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 20,35</t>
+          <t>4,55; 20,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 24,85</t>
+          <t>4,33; 25,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,87</t>
+          <t>1,7; 14,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,92</t>
+          <t>0,0; 78,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 35,64</t>
+          <t>6,39; 35,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,99</t>
+          <t>0,0; 22,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 37,66</t>
+          <t>3,82; 38,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,82</t>
+          <t>0,0; 47,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 28,01</t>
+          <t>3,22; 26,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,23</t>
+          <t>0,0; 40,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 21,42</t>
+          <t>2,44; 22,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 51,66</t>
+          <t>6,07; 50,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 24,23</t>
+          <t>6,59; 25,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 21,18</t>
+          <t>2,76; 23,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 23,24</t>
+          <t>6,03; 22,73</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,06</t>
+          <t>0,0; 22,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,22</t>
+          <t>0,0; 11,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,43; 32,9</t>
+          <t>3,94; 31,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,08</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 20,79</t>
+          <t>2,36; 20,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 17,7</t>
+          <t>1,47; 16,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,0</t>
+          <t>0,0; 29,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 12,21</t>
+          <t>2,1; 11,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 19,6</t>
+          <t>3,97; 19,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,06</t>
+          <t>0,0; 15,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 34,03</t>
+          <t>7,39; 33,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,16; 64,88</t>
+          <t>8,11; 58,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 54,53</t>
+          <t>7,02; 52,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 36,83</t>
+          <t>7,19; 38,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 66,96</t>
+          <t>13,0; 65,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 23,93</t>
+          <t>4,26; 24,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 29,19</t>
+          <t>9,49; 28,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 53,28</t>
+          <t>14,4; 52,92</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,55</t>
+          <t>0,0; 26,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,72</t>
+          <t>0,0; 33,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,08</t>
+          <t>0,0; 25,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,68</t>
+          <t>0,0; 19,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,31</t>
+          <t>0,0; 30,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,53</t>
+          <t>0,0; 34,69</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,77</t>
+          <t>0,0; 71,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 32,45</t>
+          <t>3,01; 34,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,54; 39,19</t>
+          <t>11,41; 38,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,0</t>
+          <t>0,0; 39,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,4</t>
+          <t>0,0; 15,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 25,31</t>
+          <t>2,84; 22,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,16; 23,0</t>
+          <t>5,22; 22,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 43,48</t>
+          <t>5,52; 52,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,58</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 21,43</t>
+          <t>3,97; 21,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,94; 26,03</t>
+          <t>9,76; 27,0</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,17; 39,11</t>
+          <t>6,82; 40,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 14,75</t>
+          <t>1,45; 14,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 28,23</t>
+          <t>0,0; 27,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,91; 26,73</t>
+          <t>4,69; 26,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,32</t>
+          <t>0,0; 11,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 28,24</t>
+          <t>3,68; 31,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,39; 17,9</t>
+          <t>4,63; 17,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 23,45</t>
+          <t>4,06; 23,63</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 10,48</t>
+          <t>1,71; 10,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 23,58</t>
+          <t>5,38; 22,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 18,18</t>
+          <t>6,21; 17,95</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,91; 31,13</t>
+          <t>4,03; 32,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,09; 47,45</t>
+          <t>8,52; 50,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,16; 39,76</t>
+          <t>8,65; 38,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 42,33</t>
+          <t>7,91; 40,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,37</t>
+          <t>0,0; 22,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,18; 36,14</t>
+          <t>4,2; 36,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,7; 21,24</t>
+          <t>2,83; 20,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,45; 20,49</t>
+          <t>3,5; 20,03</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,38; 33,59</t>
+          <t>8,89; 33,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,54; 22,6</t>
+          <t>5,07; 22,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,11; 26,64</t>
+          <t>8,45; 25,73</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,29; 21,8</t>
+          <t>8,34; 22,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,23</t>
+          <t>5,57; 12,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,22; 16,05</t>
+          <t>7,27; 16,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,21; 22,01</t>
+          <t>11,2; 23,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,86</t>
+          <t>1,89; 12,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,83</t>
+          <t>4,92; 12,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,6; 16,52</t>
+          <t>6,48; 16,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,93; 16,86</t>
+          <t>8,2; 17,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,36; 15,32</t>
+          <t>6,68; 15,4</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,68</t>
+          <t>6,04; 10,88</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,95; 14,74</t>
+          <t>8,0; 14,66</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,86; 17,97</t>
+          <t>10,83; 17,61</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5642</t>
+          <t>0; 4829</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1690; 10345</t>
+          <t>1616; 9499</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1824</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6321</t>
+          <t>0; 6098</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6402</t>
+          <t>0; 6522</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2254; 12285</t>
+          <t>2181; 11728</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>456; 4543</t>
+          <t>473; 4384</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5154</t>
+          <t>0; 5950</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2737; 13160</t>
+          <t>2943; 12954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2082; 12277</t>
+          <t>2138; 12414</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>968; 8488</t>
+          <t>969; 8530</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6354</t>
+          <t>0; 6133</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1990; 11076</t>
+          <t>1985; 11183</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5629</t>
+          <t>0; 4347</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1528; 9167</t>
+          <t>930; 9350</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4018</t>
+          <t>0; 4230</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>986; 8475</t>
+          <t>974; 7968</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6546</t>
+          <t>0; 6497</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>782; 7147</t>
+          <t>814; 7412</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1022; 8686</t>
+          <t>1020; 8511</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4198; 14865</t>
+          <t>4045; 15867</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>948; 7475</t>
+          <t>975; 8363</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3530; 13411</t>
+          <t>3480; 13117</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4386</t>
+          <t>0; 4169</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5930</t>
+          <t>0; 5984</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1769</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>946; 7019</t>
+          <t>840; 6755</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3325</t>
+          <t>0; 4205</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>961; 8284</t>
+          <t>942; 8267</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1750</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>380; 4742</t>
+          <t>394; 4485</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6058</t>
+          <t>0; 6701</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1889; 11314</t>
+          <t>1943; 10754</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1817</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1817; 9432</t>
+          <t>1910; 9307</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1612</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3982</t>
+          <t>0; 4698</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2712; 13065</t>
+          <t>2837; 12879</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2177; 15410</t>
+          <t>1926; 13920</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1672</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1172; 8956</t>
+          <t>1153; 8693</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2482; 13397</t>
+          <t>2614; 14161</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2157; 12195</t>
+          <t>2367; 11841</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1699</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1929; 11226</t>
+          <t>2000; 11373</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6558; 21826</t>
+          <t>7095; 21237</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5779; 22360</t>
+          <t>6041; 22208</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1701</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3497</t>
+          <t>0; 3496</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3414</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1333</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1815</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3975</t>
+          <t>0; 5006</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1486</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>123; 540</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5828</t>
+          <t>0; 6449</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3543</t>
+          <t>0; 4056</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2948</t>
+          <t>0; 2655</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6738</t>
+          <t>0; 6337</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1995</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>847; 9158</t>
+          <t>850; 9616</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2745; 10202</t>
+          <t>2971; 9997</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4983</t>
+          <t>0; 4231</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5807</t>
+          <t>0; 5580</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>960; 9228</t>
+          <t>1036; 8078</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1662; 6209</t>
+          <t>1410; 6103</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1064; 8476</t>
+          <t>1076; 10214</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 6956</t>
+          <t>0; 4436</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2784; 13859</t>
+          <t>2568; 13781</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5270; 13805</t>
+          <t>5175; 14319</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1957; 10670</t>
+          <t>1861; 10940</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>952; 9553</t>
+          <t>940; 9169</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>902; 7463</t>
+          <t>0; 7290</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2132; 11613</t>
+          <t>2038; 11493</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1839</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 7353</t>
+          <t>0; 6650</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1004; 7739</t>
+          <t>1009; 8535</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2201; 8971</t>
+          <t>2321; 8792</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1821; 10719</t>
+          <t>1857; 10798</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2021; 13041</t>
+          <t>2124; 13223</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2929; 12695</t>
+          <t>2897; 12342</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5422; 17006</t>
+          <t>5811; 16788</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1032; 8214</t>
+          <t>1064; 8624</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2183; 11395</t>
+          <t>2046; 12149</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3170; 13760</t>
+          <t>2994; 13281</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2120; 10986</t>
+          <t>2054; 10487</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6565</t>
+          <t>0; 6014</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1057; 9148</t>
+          <t>1062; 9165</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>773; 6077</t>
+          <t>811; 5971</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1841; 10928</t>
+          <t>1864; 10681</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4626; 16567</t>
+          <t>4387; 16690</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3401; 13866</t>
+          <t>3109; 14065</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4426; 14535</t>
+          <t>4611; 14038</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10199; 26830</t>
+          <t>10271; 27270</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15289; 34716</t>
+          <t>15800; 35781</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14421; 32040</t>
+          <t>14519; 32869</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22434; 44043</t>
+          <t>22408; 46561</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1180; 10186</t>
+          <t>1777; 11797</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12527; 30078</t>
+          <t>12509; 31099</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12554; 31425</t>
+          <t>12332; 30864</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>16941; 36007</t>
+          <t>17521; 36713</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13786; 33224</t>
+          <t>14495; 33396</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31596; 57467</t>
+          <t>32517; 58572</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30994; 57455</t>
+          <t>31206; 57173</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>44915; 74353</t>
+          <t>44812; 72856</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$ingresado-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15D$ingresado-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,95</t>
+          <t>0,0; 61,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 25,65</t>
+          <t>4,62; 27,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,71</t>
+          <t>0,0; 22,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,61</t>
+          <t>0,0; 21,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 38,85</t>
+          <t>7,46; 37,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 15,13</t>
+          <t>1,55; 13,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,32</t>
+          <t>0,0; 31,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 20,03</t>
+          <t>4,51; 20,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 25,13</t>
+          <t>4,3; 25,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,95</t>
+          <t>1,63; 12,94</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,1</t>
+          <t>0,0; 78,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 35,98</t>
+          <t>6,28; 36,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,39</t>
+          <t>0,0; 21,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 38,41</t>
+          <t>6,48; 37,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,19</t>
+          <t>0,0; 46,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 26,34</t>
+          <t>0,0; 24,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,92</t>
+          <t>0,0; 40,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 22,22</t>
+          <t>3,26; 20,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 50,62</t>
+          <t>6,13; 52,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 25,87</t>
+          <t>6,37; 24,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 23,7</t>
+          <t>2,78; 21,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 22,73</t>
+          <t>6,56; 22,87</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,87</t>
+          <t>0,0; 24,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,32</t>
+          <t>0,0; 13,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 31,67</t>
+          <t>4,17; 31,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 79,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 20,75</t>
+          <t>2,42; 19,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 16,74</t>
+          <t>1,39; 17,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,87</t>
+          <t>0,0; 26,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,6</t>
+          <t>2,09; 10,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 19,34</t>
+          <t>3,85; 18,5</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,4</t>
+          <t>0,0; 13,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 33,55</t>
+          <t>7,58; 32,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 58,61</t>
+          <t>8,69; 61,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 52,93</t>
+          <t>6,99; 52,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 38,93</t>
+          <t>6,83; 34,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,0; 65,02</t>
+          <t>11,48; 67,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 24,24</t>
+          <t>4,32; 24,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 28,41</t>
+          <t>9,32; 28,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,4; 52,92</t>
+          <t>14,8; 52,88</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,54</t>
+          <t>0,0; 33,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,55</t>
+          <t>0,0; 33,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,28</t>
+          <t>0,0; 22,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,56</t>
+          <t>0,0; 19,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,12</t>
+          <t>0,0; 25,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,69</t>
+          <t>0,0; 32,19</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,26</t>
+          <t>0,0; 72,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 34,07</t>
+          <t>3,01; 31,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,41; 38,4</t>
+          <t>11,26; 38,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,91</t>
+          <t>0,0; 48,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,76</t>
+          <t>0,0; 14,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,84; 22,16</t>
+          <t>2,86; 25,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,22; 22,6</t>
+          <t>5,24; 21,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 52,39</t>
+          <t>5,44; 46,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,97; 21,31</t>
+          <t>4,53; 22,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,76; 27,0</t>
+          <t>10,68; 25,55</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 40,1</t>
+          <t>6,27; 37,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 14,16</t>
+          <t>1,47; 15,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,58</t>
+          <t>3,39; 28,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,69; 26,46</t>
+          <t>5,71; 26,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,14</t>
+          <t>0,0; 12,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 31,14</t>
+          <t>3,47; 28,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 17,55</t>
+          <t>4,56; 17,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 23,63</t>
+          <t>4,13; 24,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 10,63</t>
+          <t>1,64; 10,16</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,38; 22,92</t>
+          <t>5,24; 21,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 17,95</t>
+          <t>6,81; 18,66</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -1697,32 +1697,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,03; 32,68</t>
+          <t>3,97; 30,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,52; 50,59</t>
+          <t>8,55; 49,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,65; 38,38</t>
+          <t>8,99; 38,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,91; 40,4</t>
+          <t>8,12; 40,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,33</t>
+          <t>0,0; 23,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,2; 36,21</t>
+          <t>4,09; 34,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,27 +1732,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,83; 20,87</t>
+          <t>3,94; 22,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,5; 20,03</t>
+          <t>3,68; 21,71</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 33,84</t>
+          <t>8,48; 33,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,07; 22,93</t>
+          <t>4,69; 22,74</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,45; 25,73</t>
+          <t>8,98; 27,99</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,34; 22,16</t>
+          <t>7,97; 22,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,57; 12,61</t>
+          <t>5,44; 12,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,46</t>
+          <t>6,93; 16,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,2; 23,27</t>
+          <t>11,57; 22,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,58</t>
+          <t>2,01; 11,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,23</t>
+          <t>5,32; 12,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,48; 16,22</t>
+          <t>6,92; 16,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,2; 17,19</t>
+          <t>8,29; 16,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,68; 15,4</t>
+          <t>6,56; 15,27</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,88</t>
+          <t>5,99; 10,77</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,66</t>
+          <t>8,15; 14,55</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,83; 17,61</t>
+          <t>11,15; 17,78</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3011</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4829</t>
+          <t>0; 5744</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1616; 9499</t>
+          <t>1711; 10109</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6098</t>
+          <t>0; 6060</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6522</t>
+          <t>0; 6074</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2181; 11728</t>
+          <t>2253; 11384</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>473; 4384</t>
+          <t>471; 4219</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5950</t>
+          <t>0; 5209</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2943; 12954</t>
+          <t>2918; 13133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2138; 12414</t>
+          <t>2123; 12565</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>969; 8530</t>
+          <t>939; 7435</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7827</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6133</t>
+          <t>0; 6184</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1985; 11183</t>
+          <t>1952; 11211</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4347</t>
+          <t>0; 4251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>930; 9350</t>
+          <t>1600; 9260</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4230</t>
+          <t>0; 4135</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>974; 7968</t>
+          <t>0; 7520</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6497</t>
+          <t>0; 6494</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>814; 7412</t>
+          <t>1131; 7209</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1020; 8511</t>
+          <t>1031; 8797</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4045; 15867</t>
+          <t>3909; 14824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>975; 8363</t>
+          <t>979; 7688</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3480; 13117</t>
+          <t>3898; 13594</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4725</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4169</t>
+          <t>0; 4539</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5984</t>
+          <t>0; 6894</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>840; 6755</t>
+          <t>931; 7059</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4205</t>
+          <t>0; 3325</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>942; 8267</t>
+          <t>965; 7893</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>394; 4485</t>
+          <t>371; 4560</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6701</t>
+          <t>0; 5845</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1943; 10754</t>
+          <t>1934; 10052</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1910; 9307</t>
+          <t>1886; 9068</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>14192</t>
         </is>
       </c>
     </row>
@@ -2838,17 +2838,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4698</t>
+          <t>0; 4128</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2837; 12879</t>
+          <t>2912; 12346</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1926; 13920</t>
+          <t>2441; 17149</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1153; 8693</t>
+          <t>1148; 8628</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2614; 14161</t>
+          <t>2486; 12725</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2367; 11841</t>
+          <t>2226; 13142</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2878,17 +2878,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2000; 11373</t>
+          <t>2025; 11325</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7095; 21237</t>
+          <t>6968; 21416</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6041; 22208</t>
+          <t>7028; 25116</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3046,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3496</t>
+          <t>0; 4401</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3397</t>
+          <t>0; 3412</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5006</t>
+          <t>0; 4424</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6449</t>
+          <t>0; 6331</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4056</t>
+          <t>0; 3470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2655</t>
+          <t>0; 2580</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9308</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6337</t>
+          <t>0; 6470</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3259,52 +3259,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>850; 9616</t>
+          <t>850; 8779</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2971; 9997</t>
+          <t>2929; 10031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4231</t>
+          <t>0; 5135</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5580</t>
+          <t>0; 5134</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1036; 8078</t>
+          <t>1043; 9173</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1410; 6103</t>
+          <t>1474; 5976</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1076; 10214</t>
+          <t>1060; 9011</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4436</t>
+          <t>0; 4554</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2568; 13781</t>
+          <t>2928; 14504</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5175; 14319</t>
+          <t>5782; 13835</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>13229</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1861; 10940</t>
+          <t>1712; 10159</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>940; 9169</t>
+          <t>955; 9958</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7290</t>
+          <t>895; 7414</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2038; 11493</t>
+          <t>3188; 15035</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6650</t>
+          <t>0; 7425</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1009; 8535</t>
+          <t>951; 7756</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2321; 8792</t>
+          <t>2666; 10502</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1857; 10798</t>
+          <t>1889; 11296</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2124; 13223</t>
+          <t>2038; 12642</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2897; 12342</t>
+          <t>2823; 11839</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5811; 16788</t>
+          <t>7777; 21319</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>10097</t>
         </is>
       </c>
     </row>
@@ -3665,32 +3665,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1064; 8624</t>
+          <t>1049; 8083</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2046; 12149</t>
+          <t>2052; 11836</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2994; 13281</t>
+          <t>3111; 13219</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2054; 10487</t>
+          <t>2401; 12079</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6014</t>
+          <t>0; 6232</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1062; 9165</t>
+          <t>1035; 8669</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>811; 5971</t>
+          <t>1333; 7642</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1864; 10681</t>
+          <t>1960; 11578</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4387; 16690</t>
+          <t>4181; 16616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3109; 14065</t>
+          <t>2879; 13952</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4611; 14038</t>
+          <t>5691; 17740</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>62913</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10271; 27270</t>
+          <t>9806; 27330</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15800; 35781</t>
+          <t>15444; 35229</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14519; 32869</t>
+          <t>13828; 32443</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22408; 46561</t>
+          <t>25581; 49570</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1777; 11797</t>
+          <t>1882; 10619</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12509; 31099</t>
+          <t>13537; 30608</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12332; 30864</t>
+          <t>13168; 32182</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>17521; 36713</t>
+          <t>19249; 38188</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14495; 33396</t>
+          <t>14220; 33122</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32517; 58572</t>
+          <t>32220; 57975</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31206; 57173</t>
+          <t>31789; 56715</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>44812; 72856</t>
+          <t>50546; 80578</t>
         </is>
       </c>
     </row>
